--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487679_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487679_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8297</v>
+        <v>4.5384</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5546</v>
+        <v>3.1542</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2751</v>
+        <v>1.3841</v>
       </c>
       <c r="G2" t="n">
         <v>1.6697</v>
@@ -610,13 +610,13 @@
         <v>4.2687</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1467</v>
+        <v>-0.1447</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6695</v>
+        <v>0.2691</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5229</v>
+        <v>-0.4138</v>
       </c>
       <c r="V2" t="n">
         <v>4.5656</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9605</v>
+        <v>2.8054</v>
       </c>
       <c r="E3" t="n">
-        <v>4.492</v>
+        <v>3.6912</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5315</v>
+        <v>-0.8858</v>
       </c>
       <c r="G3" t="n">
         <v>3.4821</v>
@@ -688,13 +688,13 @@
         <v>1.1642</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8858</v>
+        <v>0.7307</v>
       </c>
       <c r="T3" t="n">
-        <v>1.578</v>
+        <v>0.7772</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3078</v>
+        <v>-0.0465</v>
       </c>
       <c r="V3" t="n">
         <v>-1.6015</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.28</v>
+        <v>2.0164</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08599999999999999</v>
+        <v>-0.0141</v>
       </c>
       <c r="F4" t="n">
-        <v>2.194</v>
+        <v>2.0304</v>
       </c>
       <c r="G4" t="n">
         <v>-0.7278</v>
@@ -766,13 +766,13 @@
         <v>4.4627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4854</v>
+        <v>0.2218</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5484</v>
+        <v>0.4483</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.063</v>
+        <v>-0.2265</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. PEÑA LOPEZ</t>
+          <t>D. RODRIGUEZ GARCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2508</v>
+        <v>1.5144</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0719</v>
+        <v>0.8052</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.8211</v>
+        <v>0.7093</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.1992</v>
+        <v>-3.5082</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.174</v>
+        <v>-1.2037</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9749</v>
+        <v>-2.3045</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8274</v>
+        <v>-0.7629</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.243</v>
+        <v>0.0289</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0704</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0266</v>
+        <v>-2.7452</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.931</v>
+        <v>-1.2325</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.0956</v>
+        <v>-1.5127</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9403</v>
+        <v>3.1045</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9403</v>
+        <v>4.0747</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3143</v>
+        <v>-1.0938</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2445</v>
+        <v>-0.4736</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5588</v>
+        <v>-0.6202</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1761</v>
+        <v>3.0119</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>3.0119</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1761</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. RODRIGUEZ GARCIA</t>
+          <t>O. PEÑA LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0863</v>
+        <v>-0.0406</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2959</v>
+        <v>1.6715</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3822</v>
+        <v>-1.7121</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5082</v>
+        <v>-0.1992</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2037</v>
+        <v>-1.174</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3045</v>
+        <v>0.9749</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7629</v>
+        <v>1.8274</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0289</v>
+        <v>-0.243</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7917999999999999</v>
+        <v>2.0704</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7452</v>
+        <v>-2.0266</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2325</v>
+        <v>-0.931</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.5127</v>
+        <v>-1.0956</v>
       </c>
       <c r="P6" t="n">
-        <v>3.1045</v>
+        <v>1.9403</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>4.0747</v>
+        <v>1.9403</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.522</v>
+        <v>-0.6057</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5747</v>
+        <v>-0.1559</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9473</v>
+        <v>-0.4497</v>
       </c>
       <c r="V6" t="n">
-        <v>3.0119</v>
+        <v>-1.1761</v>
       </c>
       <c r="W6" t="n">
-        <v>3.0119</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.1761</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0803</v>
+        <v>-0.053</v>
       </c>
       <c r="E7" t="n">
         <v>0.0406</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1209</v>
+        <v>-0.0936</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0984</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>A. JIMENEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4241</v>
+        <v>-0.2323</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.634</v>
+        <v>0.2187</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2098</v>
+        <v>-0.4509</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1717</v>
+        <v>-0.751</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7779</v>
+        <v>-0.0725</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3938</v>
+        <v>-0.6785</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8179999999999999</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9804</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1624</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3537</v>
+        <v>-0.751</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7975</v>
+        <v>-0.0725</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5561</v>
+        <v>-0.6785</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1344</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>3.1045</v>
+        <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3102</v>
+        <v>0.1307</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8512</v>
+        <v>0.2187</v>
       </c>
       <c r="U8" t="n">
-        <v>0.459</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.697</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-1.697</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. JIMENEZ FERNANDEZ</t>
+          <t>M. RODRÍGUEZ RIVEROL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6599</v>
+        <v>-1.2482</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1817</v>
+        <v>-0.9702</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4782</v>
+        <v>-0.278</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.751</v>
+        <v>-1.4243</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0725</v>
+        <v>-1.1518</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6785</v>
+        <v>-0.2725</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.751</v>
+        <v>-0.7569</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0725</v>
+        <v>-0.4844</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6785</v>
+        <v>-0.2725</v>
       </c>
       <c r="P9" t="n">
         <v>0.3881</v>
@@ -1156,13 +1156,13 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.297</v>
+        <v>-0.212</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1817</v>
+        <v>-0.3028</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1153</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RODRÍGUEZ RIVEROL</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3027</v>
+        <v>-1.5064</v>
       </c>
       <c r="E10" t="n">
+        <v>-3.3347</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.8283</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-2.1717</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-1.7779</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.3938</v>
+      </c>
+      <c r="J10" t="n">
+        <v>-0.8179999999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.9804</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1624</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.3537</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.7975</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.5561</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1344</v>
+      </c>
+      <c r="Q10" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="F10" t="n">
-        <v>-0.3325</v>
-      </c>
-      <c r="G10" t="n">
-        <v>-1.4243</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-1.1518</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-0.2725</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-0.6673</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.6673</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-0.7569</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.4844</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.2725</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.3881</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.3881</v>
+        <v>3.1045</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2665</v>
+        <v>0.2279</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3028</v>
+        <v>0.1505</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0363</v>
+        <v>0.0774</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.697</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-1.697</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. REBERGEN</t>
+          <t>J. RIES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0143</v>
+        <v>-1.7899</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4453</v>
+        <v>-4.1893</v>
       </c>
       <c r="F11" t="n">
-        <v>0.431</v>
+        <v>2.3994</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1715</v>
+        <v>-2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1038</v>
+        <v>0.1409</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0677</v>
+        <v>-2.5008</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2935</v>
+        <v>-2.5257</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0412</v>
+        <v>0.103</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3347</v>
+        <v>-2.6287</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1219</v>
+        <v>0.1658</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.145</v>
+        <v>0.0379</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2669</v>
+        <v>0.1279</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3881</v>
+        <v>2.3284</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2607</v>
+        <v>0.182</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1817</v>
+        <v>0.2767</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.079</v>
+        <v>-0.0948</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. OJEDA DAVILA</t>
+          <t>I. REBERGEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.0931</v>
+        <v>-1.8324</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8493</v>
+        <v>-2.3452</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7562</v>
+        <v>0.5128</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5603</v>
+        <v>-1.1715</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5322</v>
+        <v>-0.1038</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0925</v>
+        <v>-1.0677</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.4651</v>
+        <v>-1.2935</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0824</v>
+        <v>0.0412</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.5475</v>
+        <v>-1.3347</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.1219</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4498</v>
+        <v>-0.145</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.545</v>
+        <v>0.2669</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6613</v>
+        <v>-0.0788</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3039</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3573</v>
+        <v>0.0028</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. RIES</t>
+          <t>D. OJEDA DAVILA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5724</v>
+        <v>-1.9112</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.89</v>
+        <v>-2.7492</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3176</v>
+        <v>0.838</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.36</v>
+        <v>-2.5603</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1409</v>
+        <v>0.5322</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5008</v>
+        <v>-3.0925</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.5257</v>
+        <v>-2.4651</v>
       </c>
       <c r="K13" t="n">
-        <v>0.103</v>
+        <v>0.0824</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6287</v>
+        <v>-2.5475</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1658</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0379</v>
+        <v>0.4498</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1279</v>
+        <v>-0.545</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3881</v>
+        <v>-0.194</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3284</v>
+        <v>0.7761</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6005</v>
+        <v>0.8431</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.424</v>
+        <v>0.404</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1765</v>
+        <v>0.4391</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2605</v>
+        <v>2.260600000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.0213</v>
+        <v>-4.021300000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>6.281700000000001</v>
+        <v>6.2819</v>
       </c>
       <c r="G14" t="n">
         <v>-9.820599999999999</v>
@@ -1519,13 +1519,13 @@
         <v>-8.007899999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>2.933600000000001</v>
+        <v>2.9336</v>
       </c>
       <c r="K14" t="n">
         <v>3.378099999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4445000000000006</v>
+        <v>-0.4445000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-12.754</v>
@@ -1546,13 +1546,13 @@
         <v>23.2839</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2466000000000003</v>
+        <v>0.2465999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>1.5306</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2842</v>
+        <v>-1.284</v>
       </c>
       <c r="V14" t="n">
         <v>3.1029</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8549</v>
+        <v>4.3723</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2248</v>
+        <v>4.1237</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6301</v>
+        <v>0.2485</v>
       </c>
       <c r="G15" t="n">
         <v>4.2821</v>
@@ -1624,13 +1624,13 @@
         <v>1.1642</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4251</v>
+        <v>0.9424</v>
       </c>
       <c r="T15" t="n">
-        <v>2.0637</v>
+        <v>0.9626</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3614</v>
+        <v>-0.0202</v>
       </c>
       <c r="V15" t="n">
         <v>0.894</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6118</v>
+        <v>4.1029</v>
       </c>
       <c r="E16" t="n">
-        <v>3.4651</v>
+        <v>3.7654</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1468</v>
+        <v>0.3376</v>
       </c>
       <c r="G16" t="n">
         <v>4.2002</v>
@@ -1702,13 +1702,13 @@
         <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1705</v>
+        <v>-0.6794</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3634</v>
+        <v>-0.0631</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8071</v>
+        <v>-0.6163</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.5111</v>
+        <v>2.8198</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5835</v>
+        <v>1.083</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9276</v>
+        <v>1.7368</v>
       </c>
       <c r="G17" t="n">
         <v>2.3554</v>
@@ -1780,13 +1780,13 @@
         <v>1.5523</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4004</v>
+        <v>0.7091</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8501</v>
+        <v>0.3496</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5503</v>
+        <v>0.3595</v>
       </c>
       <c r="V17" t="n">
         <v>0.1433</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0008</v>
+        <v>1.1287</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1989</v>
+        <v>2.5993</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1981</v>
+        <v>-1.4707</v>
       </c>
       <c r="G18" t="n">
         <v>2.674</v>
@@ -1858,13 +1858,13 @@
         <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6314</v>
+        <v>-0.5036</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7268</v>
+        <v>-0.3264</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0954</v>
+        <v>-0.1772</v>
       </c>
       <c r="V18" t="n">
         <v>-2.4</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1428</v>
+        <v>0.2156</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7238</v>
+        <v>-2.6237</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8666</v>
+        <v>2.8393</v>
       </c>
       <c r="G19" t="n">
         <v>-0.9857</v>
@@ -1936,13 +1936,13 @@
         <v>2.1344</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2133</v>
+        <v>-0.1405</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0617</v>
+        <v>0.1618</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.275</v>
+        <v>-0.3022</v>
       </c>
       <c r="V19" t="n">
         <v>2.1179</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6168</v>
+        <v>-1.0267</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1044</v>
+        <v>0.5038</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7212</v>
+        <v>-1.5304</v>
       </c>
       <c r="G20" t="n">
         <v>1.8277</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.4576</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.3707</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1038</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="V20" t="n">
         <v>-2.7298</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8512</v>
+        <v>-1.4513</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6528</v>
+        <v>-1.9531</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8016</v>
+        <v>0.5018</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2016</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3206</v>
+        <v>-0.2795</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2434</v>
+        <v>-0.0569</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0772</v>
+        <v>-0.2226</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4926</v>
+        <v>-1.5922</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4549</v>
+        <v>-2.8543</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9623</v>
+        <v>1.2621</v>
       </c>
       <c r="G22" t="n">
         <v>0.8001</v>
@@ -2170,13 +2170,13 @@
         <v>2.5224</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9643</v>
+        <v>-0.0639</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3017</v>
+        <v>0.2989</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6626</v>
+        <v>-0.3628</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7841</v>
+        <v>-4.3658</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3825</v>
+        <v>-4.1823</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4015</v>
+        <v>-0.1835</v>
       </c>
       <c r="G23" t="n">
         <v>-2.4571</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5404</v>
+        <v>-1.1221</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7874</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.753</v>
+        <v>-0.535</v>
       </c>
       <c r="V23" t="n">
         <v>0.3776</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.6372</v>
+        <v>-6.4638</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.6443</v>
+        <v>-6.7434</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0071</v>
+        <v>0.2796</v>
       </c>
       <c r="G24" t="n">
         <v>-2.6746</v>
@@ -2326,13 +2326,13 @@
         <v>2.1344</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7402</v>
+        <v>0.4332</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7268</v>
+        <v>0.1741</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0134</v>
+        <v>0.2591</v>
       </c>
       <c r="V24" t="n">
         <v>-1.506</v>
@@ -2362,10 +2362,10 @@
         <v>-2.2605</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2816</v>
+        <v>-6.281599999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>4.0213</v>
+        <v>4.0211</v>
       </c>
       <c r="G25" t="n">
         <v>9.820499999999997</v>
@@ -2404,13 +2404,13 @@
         <v>14.5525</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2466000000000002</v>
+        <v>-0.2467000000000002</v>
       </c>
       <c r="T25" t="n">
         <v>1.2841</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.5306</v>
+        <v>-1.5308</v>
       </c>
       <c r="V25" t="n">
         <v>-3.103</v>
